--- a/results/reports/year_2022_report.xlsx
+++ b/results/reports/year_2022_report.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,30 +505,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return_compounded</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>top_30_excess</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>decile_return_compounded</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>decile_excess</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>OMXS30_return</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>OMXC25_return</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>OMXH25_return</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>OSEBX_return</t>
         </is>
@@ -572,21 +582,27 @@
         <v>40.36</v>
       </c>
       <c r="M2" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="N2" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="O2" t="n">
         <v>12.24</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>34.32</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>-15.55</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>-13.49</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>-13.4</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>-1.03</v>
       </c>
     </row>
@@ -667,7 +683,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6415278294016841</v>
+        <v>0.6415278294016842</v>
       </c>
       <c r="E3" t="n">
         <v>20.4239</v>
@@ -727,7 +743,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6258431266629462</v>
+        <v>0.6258431266629463</v>
       </c>
       <c r="E6" t="n">
         <v>1.448</v>
@@ -787,7 +803,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6070754147706784</v>
+        <v>0.6070754147706782</v>
       </c>
       <c r="E9" t="n">
         <v>-10.119</v>
@@ -807,7 +823,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6047781679402272</v>
+        <v>0.6047781679402271</v>
       </c>
       <c r="E10" t="n">
         <v>-9.1228</v>
@@ -907,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5938719204575601</v>
+        <v>0.5938719204575602</v>
       </c>
       <c r="E15" t="n">
         <v>-3.0952</v>
@@ -927,7 +943,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5922931035242744</v>
+        <v>0.5922931035242746</v>
       </c>
       <c r="E16" t="n">
         <v>-3.403</v>
@@ -1133,7 +1149,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6513140465419986</v>
+        <v>0.6513140465419989</v>
       </c>
       <c r="E4" t="n">
         <v>-14.0442</v>
@@ -1153,7 +1169,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6484747834169865</v>
+        <v>0.6484747834169863</v>
       </c>
       <c r="E5" t="n">
         <v>-15.3555</v>
@@ -1193,7 +1209,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6394126399172971</v>
+        <v>0.639412639917297</v>
       </c>
       <c r="E7" t="n">
         <v>-8.7583</v>
@@ -1213,7 +1229,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6350266251382155</v>
+        <v>0.6350266251382156</v>
       </c>
       <c r="E8" t="n">
         <v>-4.8725</v>
@@ -1253,7 +1269,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6320694748640947</v>
+        <v>0.6320694748640948</v>
       </c>
       <c r="E10" t="n">
         <v>-9.4724</v>
@@ -1313,7 +1329,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6236565103639298</v>
+        <v>0.6236565103639299</v>
       </c>
       <c r="E13" t="n">
         <v>-1.9126</v>
@@ -1333,7 +1349,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6229959593662736</v>
+        <v>0.6229959593662735</v>
       </c>
       <c r="E14" t="n">
         <v>-9.9297</v>
@@ -1433,7 +1449,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6130862058850522</v>
+        <v>0.6130862058850524</v>
       </c>
       <c r="E19" t="n">
         <v>-9.6745</v>
@@ -1539,7 +1555,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.667922523005765</v>
+        <v>0.6679225230057653</v>
       </c>
       <c r="E2" t="n">
         <v>9.946400000000001</v>
@@ -1579,7 +1595,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6389310266835125</v>
+        <v>0.6389310266835124</v>
       </c>
       <c r="E4" t="n">
         <v>-0.995</v>
@@ -1599,7 +1615,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6343156893837079</v>
+        <v>0.6343156893837077</v>
       </c>
       <c r="E5" t="n">
         <v>-3.3639</v>
@@ -1619,7 +1635,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6333810095049223</v>
+        <v>0.6333810095049222</v>
       </c>
       <c r="E6" t="n">
         <v>-0.8333</v>
@@ -1639,7 +1655,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6319388576340158</v>
+        <v>0.6319388576340156</v>
       </c>
       <c r="E7" t="n">
         <v>10.2365</v>
@@ -1659,7 +1675,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.630315271872974</v>
+        <v>0.6303152718729739</v>
       </c>
       <c r="E8" t="n">
         <v>10.3559</v>
@@ -1739,7 +1755,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6235866962991643</v>
+        <v>0.6235866962991644</v>
       </c>
       <c r="E12" t="n">
         <v>6.6095</v>
@@ -1759,7 +1775,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6232800251821341</v>
+        <v>0.623280025182134</v>
       </c>
       <c r="E13" t="n">
         <v>4.7619</v>
@@ -1799,7 +1815,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6166765610764476</v>
+        <v>0.6166765610764475</v>
       </c>
       <c r="E15" t="n">
         <v>-0.5</v>
@@ -1819,7 +1835,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6161233244591858</v>
+        <v>0.6161233244591857</v>
       </c>
       <c r="E16" t="n">
         <v>9.550599999999999</v>
@@ -1839,7 +1855,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6155864400965447</v>
+        <v>0.6155864400965446</v>
       </c>
       <c r="E17" t="n">
         <v>-2.3222</v>
@@ -2065,7 +2081,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6287534423297519</v>
+        <v>0.6287534423297518</v>
       </c>
       <c r="E6" t="n">
         <v>2.7578</v>
@@ -2125,7 +2141,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6229513210562042</v>
+        <v>0.6229513210562041</v>
       </c>
       <c r="E9" t="n">
         <v>0.4747</v>
@@ -2165,7 +2181,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6161524906189628</v>
+        <v>0.6161524906189629</v>
       </c>
       <c r="E11" t="n">
         <v>0.2404</v>
@@ -2205,7 +2221,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6130447588563822</v>
+        <v>0.6130447588563821</v>
       </c>
       <c r="E13" t="n">
         <v>10.2313</v>
@@ -2225,7 +2241,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6097865705271253</v>
+        <v>0.6097865705271251</v>
       </c>
       <c r="E14" t="n">
         <v>3.0622</v>
@@ -2265,7 +2281,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6033123257055025</v>
+        <v>0.6033123257055026</v>
       </c>
       <c r="E16" t="n">
         <v>4.0668</v>
@@ -2285,7 +2301,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5992885420224764</v>
+        <v>0.5992885420224765</v>
       </c>
       <c r="E17" t="n">
         <v>3.23</v>
@@ -2305,7 +2321,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5990711707245883</v>
+        <v>0.5990711707245884</v>
       </c>
       <c r="E18" t="n">
         <v>5.7851</v>
@@ -2345,7 +2361,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.594381373404447</v>
+        <v>0.5943813734044469</v>
       </c>
       <c r="E20" t="n">
         <v>14.4122</v>
@@ -2611,7 +2627,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6182116271174337</v>
+        <v>0.6182116271174336</v>
       </c>
       <c r="E11" t="n">
         <v>0.5846</v>
@@ -2631,7 +2647,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6172685960587508</v>
+        <v>0.617268596058751</v>
       </c>
       <c r="E12" t="n">
         <v>1.2477</v>
@@ -2671,7 +2687,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6151258443377534</v>
+        <v>0.6151258443377535</v>
       </c>
       <c r="E14" t="n">
         <v>1.865</v>
@@ -2711,7 +2727,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6131571166506645</v>
+        <v>0.6131571166506644</v>
       </c>
       <c r="E16" t="n">
         <v>4.8148</v>
@@ -2731,7 +2747,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6129634326664676</v>
+        <v>0.6129634326664677</v>
       </c>
       <c r="E17" t="n">
         <v>-3.6058</v>
@@ -2751,7 +2767,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.612479365549624</v>
+        <v>0.6124793655496239</v>
       </c>
       <c r="E18" t="n">
         <v>2.0434</v>
@@ -2771,7 +2787,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.612160745463281</v>
+        <v>0.6121607454632809</v>
       </c>
       <c r="E19" t="n">
         <v>-2.1193</v>
@@ -2811,7 +2827,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6115288018295029</v>
+        <v>0.6115288018295028</v>
       </c>
       <c r="E21" t="n">
         <v>20.8095</v>
@@ -2877,7 +2893,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6985385621081203</v>
+        <v>0.6985385621081204</v>
       </c>
       <c r="E2" t="n">
         <v>14.3411</v>
@@ -2977,7 +2993,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6454614976248405</v>
+        <v>0.6454614976248404</v>
       </c>
       <c r="E7" t="n">
         <v>13.1122</v>
@@ -3057,7 +3073,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6393158692333416</v>
+        <v>0.6393158692333415</v>
       </c>
       <c r="E11" t="n">
         <v>7.5723</v>
@@ -3097,7 +3113,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6336664520659738</v>
+        <v>0.6336664520659737</v>
       </c>
       <c r="E13" t="n">
         <v>-2.8684</v>
@@ -3197,7 +3213,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6279704698008644</v>
+        <v>0.6279704698008645</v>
       </c>
       <c r="E18" t="n">
         <v>13.6071</v>
@@ -3277,7 +3293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3298,25 +3314,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>decile_return</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>OMXS30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>OMXC25</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>OMXH25</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OSEBX</t>
         </is>
@@ -3333,18 +3354,21 @@
         <v>-3.13</v>
       </c>
       <c r="D2" t="n">
+        <v>-3.43</v>
+      </c>
+      <c r="E2" t="n">
         <v>-3.95</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>-5.35</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>-9.640000000000001</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>-4.85</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>-2.21</v>
       </c>
     </row>
@@ -3359,18 +3383,21 @@
         <v>4.97</v>
       </c>
       <c r="D3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="E3" t="n">
         <v>3.61</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>-6.82</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>-0.64</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>-7.73</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>2.32</v>
       </c>
     </row>
@@ -3385,18 +3412,21 @@
         <v>-0.15</v>
       </c>
       <c r="D4" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E4" t="n">
         <v>-0.27</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>-1.82</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1.21</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>-0.54</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>4.92</v>
       </c>
     </row>
@@ -3411,18 +3441,21 @@
         <v>-2.7</v>
       </c>
       <c r="D5" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="E5" t="n">
         <v>-1.95</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>-1.73</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.36</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>-1.71</v>
       </c>
     </row>
@@ -3437,18 +3470,21 @@
         <v>-5.46</v>
       </c>
       <c r="D6" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="E6" t="n">
         <v>-5.89</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-0.79</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>-4.67</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-0.48</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>3.84</v>
       </c>
     </row>
@@ -3463,18 +3499,21 @@
         <v>3.6</v>
       </c>
       <c r="D7" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="E7" t="n">
         <v>6.6</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>-8.32</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>-6.39</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>-7.5</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>-9.1</v>
       </c>
     </row>
@@ -3489,18 +3528,21 @@
         <v>0.31</v>
       </c>
       <c r="D8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E8" t="n">
         <v>-2.35</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>8.539999999999999</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>12.44</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>6.69</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>7.08</v>
       </c>
     </row>
@@ -3515,18 +3557,21 @@
         <v>-6.35</v>
       </c>
       <c r="D9" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="E9" t="n">
         <v>-5.41</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>-5.53</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>-6.66</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>-1.95</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>-0.36</v>
       </c>
     </row>
@@ -3541,18 +3586,21 @@
         <v>3.26</v>
       </c>
       <c r="D10" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E10" t="n">
         <v>5.19</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-4.75</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-12.92</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>-6.8</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>-11.68</v>
       </c>
     </row>
@@ -3567,18 +3615,21 @@
         <v>7.46</v>
       </c>
       <c r="D11" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="E11" t="n">
         <v>8.34</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>7.63</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>9.42</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>5.11</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>6.59</v>
       </c>
     </row>
@@ -3593,18 +3644,21 @@
         <v>4.05</v>
       </c>
       <c r="D12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E12" t="n">
         <v>1.24</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>6.8</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>7.11</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>6.93</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>3.85</v>
       </c>
     </row>
@@ -3619,18 +3673,21 @@
         <v>12.7</v>
       </c>
       <c r="D13" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="E13" t="n">
         <v>7.88</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>-2.81</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>0.83</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>-2.03</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>-2.6</v>
       </c>
     </row>
@@ -3977,7 +4034,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6901342248415213</v>
+        <v>0.6901342248415212</v>
       </c>
       <c r="E5" t="n">
         <v>-0.7421</v>
@@ -4077,7 +4134,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6488129349625297</v>
+        <v>0.6488129349625296</v>
       </c>
       <c r="E10" t="n">
         <v>-4.4773</v>
@@ -4177,7 +4234,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6344714217734863</v>
+        <v>0.6344714217734861</v>
       </c>
       <c r="E15" t="n">
         <v>-0.7546</v>
@@ -4237,7 +4294,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6231319457149719</v>
+        <v>0.6231319457149718</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1062</v>
@@ -4257,7 +4314,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6231033767373614</v>
+        <v>0.6231033767373613</v>
       </c>
       <c r="E19" t="n">
         <v>-14.9664</v>
@@ -4277,7 +4334,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6173345705349162</v>
+        <v>0.617334570534916</v>
       </c>
       <c r="E20" t="n">
         <v>-14.6275</v>
@@ -4297,7 +4354,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6162861798151247</v>
+        <v>0.6162861798151248</v>
       </c>
       <c r="E21" t="n">
         <v>-7.3292</v>
@@ -4403,7 +4460,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7361160907425907</v>
+        <v>0.7361160907425905</v>
       </c>
       <c r="E4" t="n">
         <v>-5.1317</v>
@@ -4503,7 +4560,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6669492425168415</v>
+        <v>0.6669492425168414</v>
       </c>
       <c r="E9" t="n">
         <v>7.7318</v>
@@ -4683,7 +4740,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6249320247265681</v>
+        <v>0.6249320247265682</v>
       </c>
       <c r="E18" t="n">
         <v>-7.5446</v>
@@ -4703,7 +4760,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6220084944006159</v>
+        <v>0.622008494400616</v>
       </c>
       <c r="E19" t="n">
         <v>14.4698</v>
@@ -4723,7 +4780,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6200893975403423</v>
+        <v>0.6200893975403424</v>
       </c>
       <c r="E20" t="n">
         <v>0.1312</v>
@@ -4889,7 +4946,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6260006601962556</v>
+        <v>0.6260006601962554</v>
       </c>
       <c r="E6" t="n">
         <v>-0.9961</v>
@@ -4929,7 +4986,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6145901339605846</v>
+        <v>0.6145901339605845</v>
       </c>
       <c r="E8" t="n">
         <v>3.31</v>
@@ -4949,7 +5006,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6136865567606014</v>
+        <v>0.6136865567606012</v>
       </c>
       <c r="E9" t="n">
         <v>-2.4155</v>
@@ -5009,7 +5066,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6036079781214035</v>
+        <v>0.6036079781214034</v>
       </c>
       <c r="E12" t="n">
         <v>12.1713</v>
@@ -5049,7 +5106,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6026771338431558</v>
+        <v>0.6026771338431557</v>
       </c>
       <c r="E14" t="n">
         <v>1.086</v>
@@ -5089,7 +5146,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5950551034308954</v>
+        <v>0.5950551034308955</v>
       </c>
       <c r="E16" t="n">
         <v>0.0539</v>
@@ -5109,7 +5166,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5909493334743156</v>
+        <v>0.5909493334743154</v>
       </c>
       <c r="E17" t="n">
         <v>-0.4608</v>
@@ -5129,7 +5186,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.585922025928205</v>
+        <v>0.5859220259282051</v>
       </c>
       <c r="E18" t="n">
         <v>4.0682</v>
@@ -5169,7 +5226,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5799150299390015</v>
+        <v>0.5799150299390016</v>
       </c>
       <c r="E20" t="n">
         <v>-12.94</v>
@@ -5255,7 +5312,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6846509689502928</v>
+        <v>0.6846509689502926</v>
       </c>
       <c r="E2" t="n">
         <v>11.284</v>
@@ -5395,7 +5452,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6242352212496458</v>
+        <v>0.6242352212496459</v>
       </c>
       <c r="E9" t="n">
         <v>-5.7828</v>
@@ -5415,7 +5472,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6214919455152487</v>
+        <v>0.6214919455152488</v>
       </c>
       <c r="E10" t="n">
         <v>-16.4817</v>
@@ -5475,7 +5532,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6132694753690535</v>
+        <v>0.6132694753690534</v>
       </c>
       <c r="E13" t="n">
         <v>-2.4558</v>
@@ -5555,7 +5612,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6060118184526953</v>
+        <v>0.6060118184526954</v>
       </c>
       <c r="E17" t="n">
         <v>-2.9605</v>
@@ -5615,7 +5672,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6015536434646073</v>
+        <v>0.6015536434646074</v>
       </c>
       <c r="E20" t="n">
         <v>-5.2063</v>
@@ -5721,7 +5778,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6461052071809591</v>
+        <v>0.646105207180959</v>
       </c>
       <c r="E3" t="n">
         <v>-0.271</v>
@@ -5821,7 +5878,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6301207012210049</v>
+        <v>0.6301207012210048</v>
       </c>
       <c r="E8" t="n">
         <v>-7.9225</v>
@@ -5961,7 +6018,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6050579397577523</v>
+        <v>0.6050579397577525</v>
       </c>
       <c r="E15" t="n">
         <v>1.7175</v>
@@ -6001,7 +6058,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6027197897512829</v>
+        <v>0.6027197897512828</v>
       </c>
       <c r="E17" t="n">
         <v>-11.7333</v>
@@ -6147,7 +6204,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6656564244331861</v>
+        <v>0.6656564244331862</v>
       </c>
       <c r="E2" t="n">
         <v>3.3397</v>
@@ -6167,7 +6224,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6621175733943937</v>
+        <v>0.6621175733943936</v>
       </c>
       <c r="E3" t="n">
         <v>6.0429</v>
@@ -6227,7 +6284,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6437233148151725</v>
+        <v>0.6437233148151723</v>
       </c>
       <c r="E6" t="n">
         <v>1.4688</v>
@@ -6267,7 +6324,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6222195023343587</v>
+        <v>0.6222195023343589</v>
       </c>
       <c r="E8" t="n">
         <v>16.2213</v>
@@ -6347,7 +6404,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.608893439578592</v>
+        <v>0.6088934395785919</v>
       </c>
       <c r="E12" t="n">
         <v>-0.4599</v>
@@ -6387,7 +6444,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.606153693973026</v>
+        <v>0.6061536939730261</v>
       </c>
       <c r="E14" t="n">
         <v>2.2881</v>
@@ -6427,7 +6484,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6034833644048979</v>
+        <v>0.6034833644048978</v>
       </c>
       <c r="E16" t="n">
         <v>0.5837</v>
@@ -6447,7 +6504,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6028976777375049</v>
+        <v>0.6028976777375048</v>
       </c>
       <c r="E17" t="n">
         <v>5.7489</v>

--- a/results/reports/year_2022_report.xlsx
+++ b/results/reports/year_2022_report.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6453669563361407</v>
+        <v>0.6453669563361408</v>
       </c>
       <c r="E2" t="n">
         <v>2.5794</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6047781679402271</v>
+        <v>0.6047781679402272</v>
       </c>
       <c r="E10" t="n">
         <v>-9.1228</v>
@@ -843,7 +843,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6035609398448044</v>
+        <v>0.6035609398448043</v>
       </c>
       <c r="E11" t="n">
         <v>16.6866</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5938719204575602</v>
+        <v>0.5938719204575601</v>
       </c>
       <c r="E15" t="n">
         <v>-3.0952</v>
@@ -943,7 +943,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5922931035242746</v>
+        <v>0.5922931035242743</v>
       </c>
       <c r="E16" t="n">
         <v>-3.403</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5916247478560515</v>
+        <v>0.5916247478560512</v>
       </c>
       <c r="E18" t="n">
         <v>-9.9147</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5897061498446923</v>
+        <v>0.5897061498446924</v>
       </c>
       <c r="E19" t="n">
         <v>0.958</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6513140465419989</v>
+        <v>0.6513140465419986</v>
       </c>
       <c r="E4" t="n">
         <v>-14.0442</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6484747834169863</v>
+        <v>0.6484747834169865</v>
       </c>
       <c r="E5" t="n">
         <v>-15.3555</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6349649354809794</v>
+        <v>0.6349649354809795</v>
       </c>
       <c r="E9" t="n">
         <v>-11.0251</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6320694748640948</v>
+        <v>0.6320694748640947</v>
       </c>
       <c r="E10" t="n">
         <v>-9.4724</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6139852997288346</v>
+        <v>0.6139852997288348</v>
       </c>
       <c r="E18" t="n">
         <v>-5.1393</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6130862058850524</v>
+        <v>0.6130862058850522</v>
       </c>
       <c r="E19" t="n">
         <v>-9.6745</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6127569010357832</v>
+        <v>0.6127569010357833</v>
       </c>
       <c r="E20" t="n">
         <v>-7.8578</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6679225230057653</v>
+        <v>0.667922523005765</v>
       </c>
       <c r="E2" t="n">
         <v>9.946400000000001</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6333810095049222</v>
+        <v>0.6333810095049223</v>
       </c>
       <c r="E6" t="n">
         <v>-0.8333</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6319388576340156</v>
+        <v>0.6319388576340158</v>
       </c>
       <c r="E7" t="n">
         <v>10.2365</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6254603291970013</v>
+        <v>0.6254603291970012</v>
       </c>
       <c r="E11" t="n">
         <v>10.608</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6235866962991644</v>
+        <v>0.6235866962991643</v>
       </c>
       <c r="E12" t="n">
         <v>6.6095</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6155864400965446</v>
+        <v>0.6155864400965447</v>
       </c>
       <c r="E17" t="n">
         <v>-2.3222</v>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6691696710284016</v>
+        <v>0.6691696710284019</v>
       </c>
       <c r="E3" t="n">
         <v>22.188</v>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6287534423297518</v>
+        <v>0.6287534423297521</v>
       </c>
       <c r="E6" t="n">
         <v>2.7578</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.628663464191905</v>
+        <v>0.6286634641919051</v>
       </c>
       <c r="E7" t="n">
         <v>10.4233</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6229513210562041</v>
+        <v>0.6229513210562042</v>
       </c>
       <c r="E9" t="n">
         <v>0.4747</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6097865705271251</v>
+        <v>0.6097865705271253</v>
       </c>
       <c r="E14" t="n">
         <v>3.0622</v>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6033123257055026</v>
+        <v>0.6033123257055025</v>
       </c>
       <c r="E16" t="n">
         <v>4.0668</v>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5992885420224765</v>
+        <v>0.5992885420224764</v>
       </c>
       <c r="E17" t="n">
         <v>3.23</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5990711707245884</v>
+        <v>0.5990711707245883</v>
       </c>
       <c r="E18" t="n">
         <v>5.7851</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5943813734044469</v>
+        <v>0.594381373404447</v>
       </c>
       <c r="E20" t="n">
         <v>14.4122</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6267897116078512</v>
+        <v>0.6267897116078514</v>
       </c>
       <c r="E8" t="n">
         <v>1.2764</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6182116271174336</v>
+        <v>0.6182116271174337</v>
       </c>
       <c r="E11" t="n">
         <v>0.5846</v>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6136839779553132</v>
+        <v>0.6136839779553133</v>
       </c>
       <c r="E15" t="n">
         <v>1.1076</v>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6131571166506644</v>
+        <v>0.6131571166506645</v>
       </c>
       <c r="E16" t="n">
         <v>4.8148</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6124793655496239</v>
+        <v>0.612479365549624</v>
       </c>
       <c r="E18" t="n">
         <v>2.0434</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6121607454632809</v>
+        <v>0.612160745463281</v>
       </c>
       <c r="E19" t="n">
         <v>-2.1193</v>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6115288018295028</v>
+        <v>0.6115288018295029</v>
       </c>
       <c r="E21" t="n">
         <v>20.8095</v>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6985385621081204</v>
+        <v>0.6985385621081203</v>
       </c>
       <c r="E2" t="n">
         <v>14.3411</v>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6655061538326449</v>
+        <v>0.6655061538326447</v>
       </c>
       <c r="E4" t="n">
         <v>28.6042</v>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6569138211853286</v>
+        <v>0.6569138211853285</v>
       </c>
       <c r="E6" t="n">
         <v>11.3776</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6393158692333415</v>
+        <v>0.6393158692333416</v>
       </c>
       <c r="E11" t="n">
         <v>7.5723</v>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6286004158301012</v>
+        <v>0.6286004158301013</v>
       </c>
       <c r="E17" t="n">
         <v>31.3268</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6279704698008645</v>
+        <v>0.6279704698008644</v>
       </c>
       <c r="E18" t="n">
         <v>13.6071</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6265935093377</v>
+        <v>0.6265935093376999</v>
       </c>
       <c r="E19" t="n">
         <v>-0.2506</v>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6235172504725762</v>
+        <v>0.6235172504725763</v>
       </c>
       <c r="E20" t="n">
         <v>31.6559</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7337449149698163</v>
+        <v>0.7337449149698165</v>
       </c>
       <c r="E2" t="n">
         <v>3.8428</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7271216468896589</v>
+        <v>0.727121646889659</v>
       </c>
       <c r="E3" t="n">
         <v>4.9677</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6901342248415212</v>
+        <v>0.6901342248415213</v>
       </c>
       <c r="E5" t="n">
         <v>-0.7421</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6894289658900483</v>
+        <v>0.6894289658900484</v>
       </c>
       <c r="E6" t="n">
         <v>1.1542</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6347491369287459</v>
+        <v>0.6347491369287458</v>
       </c>
       <c r="E14" t="n">
         <v>-4.7039</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6231033767373613</v>
+        <v>0.6231033767373614</v>
       </c>
       <c r="E19" t="n">
         <v>-14.9664</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.617334570534916</v>
+        <v>0.6173345705349161</v>
       </c>
       <c r="E20" t="n">
         <v>-14.6275</v>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7452954397506909</v>
+        <v>0.745295439750691</v>
       </c>
       <c r="E2" t="n">
         <v>8.315099999999999</v>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7399329230268625</v>
+        <v>0.7399329230268624</v>
       </c>
       <c r="E3" t="n">
         <v>-7.8752</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.7310364782934781</v>
+        <v>0.731036478293478</v>
       </c>
       <c r="E5" t="n">
         <v>-4.9932</v>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.7291414045192781</v>
+        <v>0.7291414045192779</v>
       </c>
       <c r="E6" t="n">
         <v>8.758599999999999</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6732943032808099</v>
+        <v>0.6732943032808101</v>
       </c>
       <c r="E7" t="n">
         <v>3.0581</v>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6720582268466521</v>
+        <v>0.6720582268466522</v>
       </c>
       <c r="E8" t="n">
         <v>13.3772</v>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6466934202274457</v>
+        <v>0.6466934202274459</v>
       </c>
       <c r="E12" t="n">
         <v>16.3856</v>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6425248225349044</v>
+        <v>0.6425248225349045</v>
       </c>
       <c r="E13" t="n">
         <v>2.9197</v>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.640752605933628</v>
+        <v>0.6407526059336278</v>
       </c>
       <c r="E14" t="n">
         <v>2.4306</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6303150814070176</v>
+        <v>0.6303150814070175</v>
       </c>
       <c r="E16" t="n">
         <v>31.8435</v>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6270186633196666</v>
+        <v>0.6270186633196667</v>
       </c>
       <c r="E17" t="n">
         <v>14.2657</v>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6200893975403424</v>
+        <v>0.6200893975403423</v>
       </c>
       <c r="E20" t="n">
         <v>0.1312</v>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6422111099230416</v>
+        <v>0.6422111099230418</v>
       </c>
       <c r="E2" t="n">
         <v>2.8369</v>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6260006601962554</v>
+        <v>0.6260006601962556</v>
       </c>
       <c r="E6" t="n">
         <v>-0.9961</v>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6110579634905853</v>
+        <v>0.6110579634905852</v>
       </c>
       <c r="E11" t="n">
         <v>-6.6558</v>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5950551034308955</v>
+        <v>0.5950551034308954</v>
       </c>
       <c r="E16" t="n">
         <v>0.0539</v>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5909493334743154</v>
+        <v>0.5909493334743156</v>
       </c>
       <c r="E17" t="n">
         <v>-0.4608</v>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5859220259282051</v>
+        <v>0.585922025928205</v>
       </c>
       <c r="E18" t="n">
         <v>4.0682</v>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.581177293440495</v>
+        <v>0.5811772934404948</v>
       </c>
       <c r="E19" t="n">
         <v>-5.8308</v>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5792326905823154</v>
+        <v>0.5792326905823155</v>
       </c>
       <c r="E21" t="n">
         <v>1.9757</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6846509689502926</v>
+        <v>0.6846509689502928</v>
       </c>
       <c r="E2" t="n">
         <v>11.284</v>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6328675637637019</v>
+        <v>0.632867563763702</v>
       </c>
       <c r="E5" t="n">
         <v>0.542</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6132694753690534</v>
+        <v>0.6132694753690535</v>
       </c>
       <c r="E13" t="n">
         <v>-2.4558</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6060118184526954</v>
+        <v>0.6060118184526953</v>
       </c>
       <c r="E17" t="n">
         <v>-2.9605</v>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6664468376891522</v>
+        <v>0.6664468376891525</v>
       </c>
       <c r="E2" t="n">
         <v>-7.7265</v>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6338088526173078</v>
+        <v>0.6338088526173077</v>
       </c>
       <c r="E5" t="n">
         <v>-8.503399999999999</v>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6336411956494207</v>
+        <v>0.6336411956494208</v>
       </c>
       <c r="E6" t="n">
         <v>-6.1564</v>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6301207012210048</v>
+        <v>0.6301207012210049</v>
       </c>
       <c r="E8" t="n">
         <v>-7.9225</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6086535267235745</v>
+        <v>0.6086535267235744</v>
       </c>
       <c r="E12" t="n">
         <v>-4.698</v>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6027197897512828</v>
+        <v>0.6027197897512829</v>
       </c>
       <c r="E17" t="n">
         <v>-11.7333</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6621175733943936</v>
+        <v>0.6621175733943937</v>
       </c>
       <c r="E3" t="n">
         <v>6.0429</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6457097440539357</v>
+        <v>0.6457097440539356</v>
       </c>
       <c r="E5" t="n">
         <v>-0.1745</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6222195023343589</v>
+        <v>0.6222195023343587</v>
       </c>
       <c r="E8" t="n">
         <v>16.2213</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6082111651738206</v>
+        <v>0.6082111651738205</v>
       </c>
       <c r="E13" t="n">
         <v>2.5681</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6061536939730261</v>
+        <v>0.606153693973026</v>
       </c>
       <c r="E14" t="n">
         <v>2.2881</v>

--- a/results/reports/year_2022_report.xlsx
+++ b/results/reports/year_2022_report.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6415278294016842</v>
+        <v>0.6415278294016841</v>
       </c>
       <c r="E3" t="n">
         <v>20.4239</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6022599184729862</v>
+        <v>0.6022599184729861</v>
       </c>
       <c r="E12" t="n">
         <v>1.1086</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5938719204575601</v>
+        <v>0.5938719204575602</v>
       </c>
       <c r="E15" t="n">
         <v>-3.0952</v>
@@ -943,7 +943,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5922931035242743</v>
+        <v>0.5922931035242744</v>
       </c>
       <c r="E16" t="n">
         <v>-3.403</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5921620952096468</v>
+        <v>0.5921620952096469</v>
       </c>
       <c r="E17" t="n">
         <v>1.2205</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5916247478560512</v>
+        <v>0.5916247478560515</v>
       </c>
       <c r="E18" t="n">
         <v>-9.9147</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6520365978096949</v>
+        <v>0.6520365978096947</v>
       </c>
       <c r="E3" t="n">
         <v>-11.4219</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6484747834169865</v>
+        <v>0.6484747834169863</v>
       </c>
       <c r="E5" t="n">
         <v>-15.3555</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6236565103639299</v>
+        <v>0.6236565103639298</v>
       </c>
       <c r="E13" t="n">
         <v>-1.9126</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6214239332915849</v>
+        <v>0.6214239332915847</v>
       </c>
       <c r="E15" t="n">
         <v>-4.4292</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6139852997288348</v>
+        <v>0.6139852997288345</v>
       </c>
       <c r="E18" t="n">
         <v>-5.1393</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6389310266835124</v>
+        <v>0.6389310266835125</v>
       </c>
       <c r="E4" t="n">
         <v>-0.995</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6254603291970012</v>
+        <v>0.6254603291970013</v>
       </c>
       <c r="E11" t="n">
         <v>10.608</v>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6140740739836336</v>
+        <v>0.6140740739836335</v>
       </c>
       <c r="E19" t="n">
         <v>-0.7471</v>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6691696710284019</v>
+        <v>0.6691696710284016</v>
       </c>
       <c r="E3" t="n">
         <v>22.188</v>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6287534423297521</v>
+        <v>0.6287534423297518</v>
       </c>
       <c r="E6" t="n">
         <v>2.7578</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6286634641919051</v>
+        <v>0.628663464191905</v>
       </c>
       <c r="E7" t="n">
         <v>10.4233</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6229513210562042</v>
+        <v>0.6229513210562041</v>
       </c>
       <c r="E9" t="n">
         <v>0.4747</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6222520413892806</v>
+        <v>0.6222520413892805</v>
       </c>
       <c r="E10" t="n">
         <v>1.2626</v>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6033123257055025</v>
+        <v>0.6033123257055026</v>
       </c>
       <c r="E16" t="n">
         <v>4.0668</v>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5992885420224764</v>
+        <v>0.5992885420224766</v>
       </c>
       <c r="E17" t="n">
         <v>3.23</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.594381373404447</v>
+        <v>0.5943813734044469</v>
       </c>
       <c r="E20" t="n">
         <v>14.4122</v>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6136839779553133</v>
+        <v>0.6136839779553132</v>
       </c>
       <c r="E15" t="n">
         <v>1.1076</v>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6129634326664677</v>
+        <v>0.6129634326664676</v>
       </c>
       <c r="E17" t="n">
         <v>-3.6058</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.612160745463281</v>
+        <v>0.6121607454632811</v>
       </c>
       <c r="E19" t="n">
         <v>-2.1193</v>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6115288018295029</v>
+        <v>0.6115288018295028</v>
       </c>
       <c r="E21" t="n">
         <v>20.8095</v>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6655061538326447</v>
+        <v>0.665506153832645</v>
       </c>
       <c r="E4" t="n">
         <v>28.6042</v>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6638683826809156</v>
+        <v>0.6638683826809155</v>
       </c>
       <c r="E5" t="n">
         <v>32.0448</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6449523776973238</v>
+        <v>0.6449523776973237</v>
       </c>
       <c r="E8" t="n">
         <v>36.9744</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6265935093376999</v>
+        <v>0.6265935093377</v>
       </c>
       <c r="E19" t="n">
         <v>-0.2506</v>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6204402530803923</v>
+        <v>0.6204402530803924</v>
       </c>
       <c r="E21" t="n">
         <v>9.0952</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7337449149698165</v>
+        <v>0.7337449149698163</v>
       </c>
       <c r="E2" t="n">
         <v>3.8428</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6901342248415213</v>
+        <v>0.6901342248415212</v>
       </c>
       <c r="E5" t="n">
         <v>-0.7421</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6894289658900484</v>
+        <v>0.6894289658900483</v>
       </c>
       <c r="E6" t="n">
         <v>1.1542</v>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6488129349625296</v>
+        <v>0.6488129349625297</v>
       </c>
       <c r="E10" t="n">
         <v>-4.4773</v>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6447916862263451</v>
+        <v>0.6447916862263449</v>
       </c>
       <c r="E11" t="n">
         <v>-1.1001</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6344714217734861</v>
+        <v>0.6344714217734863</v>
       </c>
       <c r="E15" t="n">
         <v>-0.7546</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6173345705349161</v>
+        <v>0.6173345705349162</v>
       </c>
       <c r="E20" t="n">
         <v>-14.6275</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7361160907425905</v>
+        <v>0.7361160907425907</v>
       </c>
       <c r="E4" t="n">
         <v>-5.1317</v>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.7291414045192779</v>
+        <v>0.7291414045192781</v>
       </c>
       <c r="E6" t="n">
         <v>8.758599999999999</v>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6720582268466522</v>
+        <v>0.6720582268466521</v>
       </c>
       <c r="E8" t="n">
         <v>13.3772</v>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6466934202274459</v>
+        <v>0.6466934202274457</v>
       </c>
       <c r="E12" t="n">
         <v>16.3856</v>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6407526059336278</v>
+        <v>0.640752605933628</v>
       </c>
       <c r="E14" t="n">
         <v>2.4306</v>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6249320247265682</v>
+        <v>0.6249320247265681</v>
       </c>
       <c r="E18" t="n">
         <v>-7.5446</v>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.622008494400616</v>
+        <v>0.6220084944006158</v>
       </c>
       <c r="E19" t="n">
         <v>14.4698</v>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6200893975403423</v>
+        <v>0.6200893975403424</v>
       </c>
       <c r="E20" t="n">
         <v>0.1312</v>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6422111099230418</v>
+        <v>0.6422111099230416</v>
       </c>
       <c r="E2" t="n">
         <v>2.8369</v>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6260006601962556</v>
+        <v>0.6260006601962553</v>
       </c>
       <c r="E6" t="n">
         <v>-0.9961</v>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5811772934404948</v>
+        <v>0.581177293440495</v>
       </c>
       <c r="E19" t="n">
         <v>-5.8308</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6846509689502928</v>
+        <v>0.6846509689502926</v>
       </c>
       <c r="E2" t="n">
         <v>11.284</v>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6520354859934149</v>
+        <v>0.652035485993415</v>
       </c>
       <c r="E3" t="n">
         <v>1.1223</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6214919455152488</v>
+        <v>0.6214919455152487</v>
       </c>
       <c r="E10" t="n">
         <v>-16.4817</v>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.619262317540262</v>
+        <v>0.6192623175402621</v>
       </c>
       <c r="E11" t="n">
         <v>-1.1945</v>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.614229107033581</v>
+        <v>0.6142291070335811</v>
       </c>
       <c r="E12" t="n">
         <v>-8.530900000000001</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6132694753690535</v>
+        <v>0.6132694753690536</v>
       </c>
       <c r="E13" t="n">
         <v>-2.4558</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6060118184526953</v>
+        <v>0.6060118184526954</v>
       </c>
       <c r="E17" t="n">
         <v>-2.9605</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6039793165104129</v>
+        <v>0.603979316510413</v>
       </c>
       <c r="E18" t="n">
         <v>-2.091</v>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6664468376891525</v>
+        <v>0.6664468376891522</v>
       </c>
       <c r="E2" t="n">
         <v>-7.7265</v>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.646105207180959</v>
+        <v>0.6461052071809591</v>
       </c>
       <c r="E3" t="n">
         <v>-0.271</v>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6336411956494208</v>
+        <v>0.6336411956494207</v>
       </c>
       <c r="E6" t="n">
         <v>-6.1564</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6086535267235744</v>
+        <v>0.6086535267235745</v>
       </c>
       <c r="E12" t="n">
         <v>-4.698</v>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6033865736936499</v>
+        <v>0.60338657369365</v>
       </c>
       <c r="E16" t="n">
         <v>4.7548</v>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6027197897512829</v>
+        <v>0.6027197897512828</v>
       </c>
       <c r="E17" t="n">
         <v>-11.7333</v>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5979242298891847</v>
+        <v>0.5979242298891848</v>
       </c>
       <c r="E18" t="n">
         <v>-26.5583</v>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5967300005215053</v>
+        <v>0.5967300005215054</v>
       </c>
       <c r="E19" t="n">
         <v>-1.0918</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6621175733943937</v>
+        <v>0.6621175733943939</v>
       </c>
       <c r="E3" t="n">
         <v>6.0429</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6222195023343587</v>
+        <v>0.6222195023343589</v>
       </c>
       <c r="E8" t="n">
         <v>16.2213</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.606153693973026</v>
+        <v>0.6061536939730261</v>
       </c>
       <c r="E14" t="n">
         <v>2.2881</v>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6028976777375048</v>
+        <v>0.6028976777375049</v>
       </c>
       <c r="E17" t="n">
         <v>5.7489</v>

--- a/results/reports/year_2022_report.xlsx
+++ b/results/reports/year_2022_report.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6453669563361408</v>
+        <v>0.6453669563361407</v>
       </c>
       <c r="E2" t="n">
         <v>2.5794</v>
@@ -743,7 +743,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6258431266629463</v>
+        <v>0.6258431266629462</v>
       </c>
       <c r="E6" t="n">
         <v>1.448</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6248776165537067</v>
+        <v>0.6248776165537065</v>
       </c>
       <c r="E7" t="n">
         <v>-6.1752</v>
@@ -803,7 +803,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6070754147706782</v>
+        <v>0.6070754147706783</v>
       </c>
       <c r="E9" t="n">
         <v>-10.119</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6047781679402272</v>
+        <v>0.6047781679402273</v>
       </c>
       <c r="E10" t="n">
         <v>-9.1228</v>
@@ -843,7 +843,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6035609398448043</v>
+        <v>0.6035609398448044</v>
       </c>
       <c r="E11" t="n">
         <v>16.6866</v>
@@ -863,7 +863,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6022599184729861</v>
+        <v>0.6022599184729862</v>
       </c>
       <c r="E12" t="n">
         <v>1.1086</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5938719204575602</v>
+        <v>0.5938719204575601</v>
       </c>
       <c r="E15" t="n">
         <v>-3.0952</v>
@@ -943,7 +943,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5922931035242744</v>
+        <v>0.5922931035242743</v>
       </c>
       <c r="E16" t="n">
         <v>-3.403</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5921620952096469</v>
+        <v>0.5921620952096468</v>
       </c>
       <c r="E17" t="n">
         <v>1.2205</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5897061498446924</v>
+        <v>0.5897061498446923</v>
       </c>
       <c r="E19" t="n">
         <v>0.958</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5876378498471705</v>
+        <v>0.5876378498471704</v>
       </c>
       <c r="E20" t="n">
         <v>7.3955</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.639412639917297</v>
+        <v>0.6394126399172971</v>
       </c>
       <c r="E7" t="n">
         <v>-8.7583</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6350266251382156</v>
+        <v>0.6350266251382155</v>
       </c>
       <c r="E8" t="n">
         <v>-4.8725</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6349649354809795</v>
+        <v>0.6349649354809794</v>
       </c>
       <c r="E9" t="n">
         <v>-11.0251</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6243877393713849</v>
+        <v>0.624387739371385</v>
       </c>
       <c r="E12" t="n">
         <v>4.5</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6236565103639298</v>
+        <v>0.6236565103639299</v>
       </c>
       <c r="E13" t="n">
         <v>-1.9126</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6214239332915847</v>
+        <v>0.6214239332915849</v>
       </c>
       <c r="E15" t="n">
         <v>-4.4292</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6139852997288345</v>
+        <v>0.6139852997288346</v>
       </c>
       <c r="E18" t="n">
         <v>-5.1393</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6127569010357833</v>
+        <v>0.6127569010357832</v>
       </c>
       <c r="E20" t="n">
         <v>-7.8578</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6389310266835125</v>
+        <v>0.6389310266835124</v>
       </c>
       <c r="E4" t="n">
         <v>-0.995</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6319388576340158</v>
+        <v>0.6319388576340157</v>
       </c>
       <c r="E7" t="n">
         <v>10.2365</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.623280025182134</v>
+        <v>0.6232800251821341</v>
       </c>
       <c r="E13" t="n">
         <v>4.7619</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6155864400965447</v>
+        <v>0.6155864400965446</v>
       </c>
       <c r="E17" t="n">
         <v>-2.3222</v>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6140740739836335</v>
+        <v>0.6140740739836336</v>
       </c>
       <c r="E19" t="n">
         <v>-0.7471</v>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6691696710284016</v>
+        <v>0.6691696710284017</v>
       </c>
       <c r="E3" t="n">
         <v>22.188</v>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6287534423297518</v>
+        <v>0.6287534423297519</v>
       </c>
       <c r="E6" t="n">
         <v>2.7578</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6229513210562041</v>
+        <v>0.6229513210562042</v>
       </c>
       <c r="E9" t="n">
         <v>0.4747</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6222520413892805</v>
+        <v>0.6222520413892806</v>
       </c>
       <c r="E10" t="n">
         <v>1.2626</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6097865705271253</v>
+        <v>0.6097865705271251</v>
       </c>
       <c r="E14" t="n">
         <v>3.0622</v>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6033123257055026</v>
+        <v>0.6033123257055027</v>
       </c>
       <c r="E16" t="n">
         <v>4.0668</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5990711707245883</v>
+        <v>0.5990711707245884</v>
       </c>
       <c r="E18" t="n">
         <v>5.7851</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5938114524009418</v>
+        <v>0.5938114524009419</v>
       </c>
       <c r="E21" t="n">
         <v>6.9444</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6706699505242422</v>
+        <v>0.6706699505242421</v>
       </c>
       <c r="E2" t="n">
         <v>4.1501</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6276856137718101</v>
+        <v>0.6276856137718102</v>
       </c>
       <c r="E6" t="n">
         <v>19.2426</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6182116271174337</v>
+        <v>0.6182116271174336</v>
       </c>
       <c r="E11" t="n">
         <v>0.5846</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6151258443377535</v>
+        <v>0.6151258443377534</v>
       </c>
       <c r="E14" t="n">
         <v>1.865</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6121607454632811</v>
+        <v>0.612160745463281</v>
       </c>
       <c r="E19" t="n">
         <v>-2.1193</v>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6115288018295028</v>
+        <v>0.6115288018295029</v>
       </c>
       <c r="E21" t="n">
         <v>20.8095</v>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.665506153832645</v>
+        <v>0.6655061538326449</v>
       </c>
       <c r="E4" t="n">
         <v>28.6042</v>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6638683826809155</v>
+        <v>0.6638683826809156</v>
       </c>
       <c r="E5" t="n">
         <v>32.0448</v>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6569138211853285</v>
+        <v>0.6569138211853286</v>
       </c>
       <c r="E6" t="n">
         <v>11.3776</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6449523776973237</v>
+        <v>0.6449523776973238</v>
       </c>
       <c r="E8" t="n">
         <v>36.9744</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6393158692333416</v>
+        <v>0.6393158692333415</v>
       </c>
       <c r="E11" t="n">
         <v>7.5723</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6392254615734551</v>
+        <v>0.6392254615734552</v>
       </c>
       <c r="E12" t="n">
         <v>0.3993</v>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6336664520659737</v>
+        <v>0.6336664520659738</v>
       </c>
       <c r="E13" t="n">
         <v>-2.8684</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6279704698008644</v>
+        <v>0.6279704698008645</v>
       </c>
       <c r="E18" t="n">
         <v>13.6071</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6901342248415212</v>
+        <v>0.6901342248415213</v>
       </c>
       <c r="E5" t="n">
         <v>-0.7421</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6894289658900483</v>
+        <v>0.6894289658900484</v>
       </c>
       <c r="E6" t="n">
         <v>1.1542</v>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6447916862263449</v>
+        <v>0.6447916862263451</v>
       </c>
       <c r="E11" t="n">
         <v>-1.1001</v>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6231319457149718</v>
+        <v>0.6231319457149719</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1062</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6173345705349162</v>
+        <v>0.6173345705349161</v>
       </c>
       <c r="E20" t="n">
         <v>-14.6275</v>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.745295439750691</v>
+        <v>0.7452954397506909</v>
       </c>
       <c r="E2" t="n">
         <v>8.315099999999999</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7361160907425907</v>
+        <v>0.7361160907425905</v>
       </c>
       <c r="E4" t="n">
         <v>-5.1317</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.731036478293478</v>
+        <v>0.7310364782934781</v>
       </c>
       <c r="E5" t="n">
         <v>-4.9932</v>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.7291414045192781</v>
+        <v>0.7291414045192779</v>
       </c>
       <c r="E6" t="n">
         <v>8.758599999999999</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6303150814070175</v>
+        <v>0.6303150814070176</v>
       </c>
       <c r="E16" t="n">
         <v>31.8435</v>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6220084944006158</v>
+        <v>0.6220084944006159</v>
       </c>
       <c r="E19" t="n">
         <v>14.4698</v>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6200893975403424</v>
+        <v>0.6200893975403422</v>
       </c>
       <c r="E20" t="n">
         <v>0.1312</v>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6110579634905852</v>
+        <v>0.6110579634905851</v>
       </c>
       <c r="E11" t="n">
         <v>-6.6558</v>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.585922025928205</v>
+        <v>0.5859220259282051</v>
       </c>
       <c r="E18" t="n">
         <v>4.0682</v>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.581177293440495</v>
+        <v>0.5811772934404948</v>
       </c>
       <c r="E19" t="n">
         <v>-5.8308</v>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5792326905823155</v>
+        <v>0.5792326905823154</v>
       </c>
       <c r="E21" t="n">
         <v>1.9757</v>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.632867563763702</v>
+        <v>0.6328675637637019</v>
       </c>
       <c r="E5" t="n">
         <v>0.542</v>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6242352212496459</v>
+        <v>0.6242352212496458</v>
       </c>
       <c r="E9" t="n">
         <v>-5.7828</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6214919455152487</v>
+        <v>0.6214919455152488</v>
       </c>
       <c r="E10" t="n">
         <v>-16.4817</v>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6192623175402621</v>
+        <v>0.619262317540262</v>
       </c>
       <c r="E11" t="n">
         <v>-1.1945</v>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6142291070335811</v>
+        <v>0.614229107033581</v>
       </c>
       <c r="E12" t="n">
         <v>-8.530900000000001</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6060118184526954</v>
+        <v>0.6060118184526953</v>
       </c>
       <c r="E17" t="n">
         <v>-2.9605</v>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.603979316510413</v>
+        <v>0.6039793165104129</v>
       </c>
       <c r="E18" t="n">
         <v>-2.091</v>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6664468376891522</v>
+        <v>0.6664468376891525</v>
       </c>
       <c r="E2" t="n">
         <v>-7.7265</v>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6461052071809591</v>
+        <v>0.646105207180959</v>
       </c>
       <c r="E3" t="n">
         <v>-0.271</v>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6392287112469824</v>
+        <v>0.6392287112469826</v>
       </c>
       <c r="E4" t="n">
         <v>-4.1667</v>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6336411956494207</v>
+        <v>0.6336411956494208</v>
       </c>
       <c r="E6" t="n">
         <v>-6.1564</v>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.60338657369365</v>
+        <v>0.6033865736936499</v>
       </c>
       <c r="E16" t="n">
         <v>4.7548</v>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6027197897512828</v>
+        <v>0.6027197897512829</v>
       </c>
       <c r="E17" t="n">
         <v>-11.7333</v>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5979242298891848</v>
+        <v>0.5979242298891847</v>
       </c>
       <c r="E18" t="n">
         <v>-26.5583</v>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6621175733943939</v>
+        <v>0.6621175733943937</v>
       </c>
       <c r="E3" t="n">
         <v>6.0429</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6457097440539356</v>
+        <v>0.6457097440539357</v>
       </c>
       <c r="E5" t="n">
         <v>-0.1745</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6437233148151723</v>
+        <v>0.6437233148151725</v>
       </c>
       <c r="E6" t="n">
         <v>1.4688</v>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6088934395785919</v>
+        <v>0.608893439578592</v>
       </c>
       <c r="E12" t="n">
         <v>-0.4599</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6082111651738205</v>
+        <v>0.6082111651738206</v>
       </c>
       <c r="E13" t="n">
         <v>2.5681</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6034833644048978</v>
+        <v>0.6034833644048979</v>
       </c>
       <c r="E16" t="n">
         <v>0.5837</v>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6028976777375049</v>
+        <v>0.6028976777375048</v>
       </c>
       <c r="E17" t="n">
         <v>5.7489</v>
